--- a/Docs/Pensão Igor 26/Pensão Igor 2026.xlsx
+++ b/Docs/Pensão Igor 26/Pensão Igor 2026.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\RGitRep\Docs\Pensão Igor 26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\R\RGitRep\Docs\Pensão Igor 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C387273C-68E1-48C4-8CE9-B80E5D9C6BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B508C14F-F10D-48CB-973C-DABA95633341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-13635" windowWidth="29040" windowHeight="15720" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Principal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Mês Pensão</t>
   </si>
@@ -54,6 +43,12 @@
   </si>
   <si>
     <t>Total pago em 2026</t>
+  </si>
+  <si>
+    <t>Pago em Março</t>
+  </si>
+  <si>
+    <t>Pago em Abril</t>
   </si>
 </sst>
 </file>
@@ -473,14 +468,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA501A0A-8321-4752-AC22-ACA6407DFB74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -491,7 +486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -502,7 +497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46082</v>
       </c>
@@ -513,61 +508,73 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B4" s="2">
+        <v>4150.45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B5" s="2">
+        <v>4150.45</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="5">
         <f>SUM(B2:B13)</f>
-        <v>7836.9</v>
+        <v>16137.8</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>5</v>

--- a/Docs/Pensão Igor 26/Pensão Igor 2026.xlsx
+++ b/Docs/Pensão Igor 26/Pensão Igor 2026.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\R\RGitRep\Docs\Pensão Igor 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B508C14F-F10D-48CB-973C-DABA95633341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483ADE8A-5E05-4419-9AEA-4DC24B8A8C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
+    <workbookView xWindow="6150" yWindow="2280" windowWidth="19815" windowHeight="11805" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Principal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Mês Pensão</t>
   </si>
@@ -49,6 +60,9 @@
   </si>
   <si>
     <t>Pago em Abril</t>
+  </si>
+  <si>
+    <t>Pago em Maio</t>
   </si>
 </sst>
 </file>
@@ -531,9 +545,15 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
+      <c r="A6" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4150.45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -574,7 +594,7 @@
       <c r="A14" s="3"/>
       <c r="B14" s="5">
         <f>SUM(B2:B13)</f>
-        <v>16137.8</v>
+        <v>20288.25</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>5</v>

--- a/Docs/Pensão Igor 26/Pensão Igor 2026.xlsx
+++ b/Docs/Pensão Igor 26/Pensão Igor 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\R\RGitRep\Docs\Pensão Igor 26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\RGitRep\Docs\Pensão Igor 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483ADE8A-5E05-4419-9AEA-4DC24B8A8C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5B71B8-0D55-431F-9A69-C65B044E8293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6150" yWindow="2280" windowWidth="19815" windowHeight="11805" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Principal" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Mês Pensão</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>Pago em Maio</t>
+  </si>
+  <si>
+    <t>Pago em Junho</t>
+  </si>
+  <si>
+    <t>Pago em Setembro</t>
+  </si>
+  <si>
+    <t>Pago em Julho</t>
   </si>
 </sst>
 </file>
@@ -482,14 +491,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA501A0A-8321-4752-AC22-ACA6407DFB74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -500,7 +509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -511,7 +520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46082</v>
       </c>
@@ -522,7 +531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46113</v>
       </c>
@@ -533,7 +542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46143</v>
       </c>
@@ -544,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46174</v>
       </c>
@@ -555,46 +564,64 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4150.45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4097.3999999999996</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B9" s="2">
+        <v>4656.1099999999997</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="5">
         <f>SUM(B2:B13)</f>
-        <v>20288.25</v>
+        <v>33192.21</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>5</v>
